--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_21.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_21.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ExamGrade</t>
+          <t>HoursSleep</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.4292879741127038</v>
+        <v>-0.1504483321141199</v>
       </c>
       <c r="C2">
-        <v>0.4834306938850738</v>
+        <v>-0.7461052388101632</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1997627782512242</v>
+        <v>-0.6354414498705463</v>
       </c>
       <c r="C3">
-        <v>-1.057979631952851</v>
+        <v>0.03188293720441232</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.2503572754240251</v>
+        <v>-0.6387054033931088</v>
       </c>
       <c r="C4">
-        <v>-0.8113539731004051</v>
+        <v>0.2199549974251676</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.62703190173597</v>
+        <v>-0.4784760450299961</v>
       </c>
       <c r="C5">
-        <v>-0.5702193048148316</v>
+        <v>-0.4443664652246407</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.3664604386734295</v>
+        <v>0.1781254086077486</v>
       </c>
       <c r="C6">
-        <v>-1.118405025037959</v>
+        <v>-0.8863467438630278</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.06474362726309792</v>
+        <v>0.5018702813589048</v>
       </c>
       <c r="C7">
-        <v>-0.1886137843885805</v>
+        <v>0.8228894831140636</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.825581811821908</v>
+        <v>1.59158685295671</v>
       </c>
       <c r="C8">
-        <v>-0.450052581695792</v>
+        <v>-1.565517992803602</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.7940436838032774</v>
+        <v>0.2962712367044008</v>
       </c>
       <c r="C9">
-        <v>-0.1266908091800193</v>
+        <v>-0.1300164358139285</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.6616398717476629</v>
+        <v>0.0660734610166724</v>
       </c>
       <c r="C10">
-        <v>-1.42972589677062</v>
+        <v>-0.02261797848178261</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>2.364198590438564</v>
+        <v>-0.230795234742192</v>
       </c>
       <c r="C11">
-        <v>-1.779628944705514</v>
+        <v>-0.20487328544471</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.8647014918149438</v>
+        <v>-0.1986468944041334</v>
       </c>
       <c r="C12">
-        <v>1.154497708844182</v>
+        <v>0.9634227953419836</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.6427766272528901</v>
+        <v>-1.60777780392404</v>
       </c>
       <c r="C13">
-        <v>1.424996063578123</v>
+        <v>-1.050202015385592</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.6656431856187967</v>
+        <v>-2.064336071568513</v>
       </c>
       <c r="C14">
-        <v>0.4264956070768555</v>
+        <v>0.6282484203205616</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.3027876925999646</v>
+        <v>-0.10705622243526</v>
       </c>
       <c r="C15">
-        <v>-1.873330989606021</v>
+        <v>-0.6289705825317218</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.4420332667002158</v>
+        <v>0.5472918285737507</v>
       </c>
       <c r="C16">
-        <v>-0.5580526045982043</v>
+        <v>-1.366931870520026</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.9758909402114945</v>
+        <v>-0.05569426261431269</v>
       </c>
       <c r="C17">
-        <v>0.6283141945505903</v>
+        <v>0.9319102590344563</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.5455428717310526</v>
+        <v>0.4584792270917997</v>
       </c>
       <c r="C18">
-        <v>-0.3097059134960981</v>
+        <v>-0.3164427913622733</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.5450808763717137</v>
+        <v>-0.6161958681443555</v>
       </c>
       <c r="C19">
-        <v>-0.06932368091234571</v>
+        <v>0.08569398804625719</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>2.239729029218607</v>
+        <v>-0.222505641429469</v>
       </c>
       <c r="C20">
-        <v>-0.2795067932723994</v>
+        <v>-0.4657318970496658</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.3915070608195245</v>
+        <v>-1.748215727577085</v>
       </c>
       <c r="C21">
-        <v>0.5755193014596051</v>
+        <v>-0.1980592056477368</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.7027540277935326</v>
+        <v>1.692987044461933</v>
       </c>
       <c r="C22">
-        <v>-0.331721664009911</v>
+        <v>-0.1966885209593156</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.208984378494807</v>
+        <v>-0.08170299889654467</v>
       </c>
       <c r="C23">
-        <v>-1.005671710725489</v>
+        <v>0.2753388908810008</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-1.623931641303406</v>
+        <v>0.1495063938533993</v>
       </c>
       <c r="C24">
-        <v>-0.03838536565549124</v>
+        <v>1.204746160707302</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.03071773149931318</v>
+        <v>0.873025509899037</v>
       </c>
       <c r="C25">
-        <v>-2.83389326090211</v>
+        <v>-0.2740801321279816</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-1.23298261474303</v>
+        <v>0.4717229368479793</v>
       </c>
       <c r="C26">
-        <v>0.01151363698818222</v>
+        <v>0.8895176095867922</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.6643431502893075</v>
+        <v>0.4887588011079659</v>
       </c>
       <c r="C27">
-        <v>1.390104701508408</v>
+        <v>-1.09845630564286</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-1.783276116395073</v>
+        <v>1.70178312226816</v>
       </c>
       <c r="C28">
-        <v>1.489382361421129</v>
+        <v>-0.2108739467842726</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.5137492460957299</v>
+        <v>-0.1656881867623949</v>
       </c>
       <c r="C29">
-        <v>-0.4722297011914421</v>
+        <v>0.5449979610508987</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.5650114184997319</v>
+        <v>-1.673079028040293</v>
       </c>
       <c r="C30">
-        <v>-0.5568137753531803</v>
+        <v>0.9842058540973158</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.1600019131547583</v>
+        <v>0.5061535613321703</v>
       </c>
       <c r="C31">
-        <v>-0.1292088905849795</v>
+        <v>-0.5737887368701015</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.705335833814383</v>
+        <v>1.006811209391542</v>
       </c>
       <c r="C32">
-        <v>2.153010752101827</v>
+        <v>-0.9249819604899949</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.590347403878686</v>
+        <v>0.6357083314843803</v>
       </c>
       <c r="C33">
-        <v>1.429489701052955</v>
+        <v>0.1218834741795776</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.7331493456569124</v>
+        <v>-0.6206936211608216</v>
       </c>
       <c r="C34">
-        <v>1.580099793526612</v>
+        <v>2.216006079097973</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>1.390764641767953</v>
+        <v>-0.3432176333388469</v>
       </c>
       <c r="C35">
-        <v>1.067403070048963</v>
+        <v>-1.129279948913953</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.7137520383259979</v>
+        <v>-0.6644177330035559</v>
       </c>
       <c r="C36">
-        <v>0.6401884092883986</v>
+        <v>-0.3931116885018763</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-2.477651990497805</v>
+        <v>-0.3656689507789491</v>
       </c>
       <c r="C37">
-        <v>0.7095007649545378</v>
+        <v>0.1776003322354361</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.3026578716307384</v>
+        <v>0.2837091240703467</v>
       </c>
       <c r="C38">
-        <v>-1.165961830448037</v>
+        <v>-0.6026938059999027</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.2090682309830336</v>
+        <v>0.3150684112004282</v>
       </c>
       <c r="C39">
-        <v>0.5231869398489563</v>
+        <v>-1.611818983561744</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.226377557553761</v>
+        <v>-1.936120114241244</v>
       </c>
       <c r="C40">
-        <v>0.9240622775687094</v>
+        <v>1.293720849257773</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.01616857727937333</v>
+        <v>0.1276632943082114</v>
       </c>
       <c r="C41">
-        <v>-0.05483319279512797</v>
+        <v>0.8240668714852976</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.7701424472722744</v>
+        <v>-1.129290388641031</v>
       </c>
       <c r="C42">
-        <v>1.240308123972801</v>
+        <v>-1.601479055071283</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.9537871380060686</v>
+        <v>0.1589393043101576</v>
       </c>
       <c r="C43">
-        <v>-0.115297689162593</v>
+        <v>-1.527435712602049</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.5901203965417732</v>
+        <v>1.467770458249065</v>
       </c>
       <c r="C44">
-        <v>-1.294189860574896</v>
+        <v>-0.296199857521001</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.9027843130034855</v>
+        <v>0.6770683012134069</v>
       </c>
       <c r="C45">
-        <v>-0.5890563950594603</v>
+        <v>0.07907604998623952</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.809705454149183</v>
+        <v>-0.4290833431858423</v>
       </c>
       <c r="C46">
-        <v>-2.510884927823006</v>
+        <v>-0.0972089261007516</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.1486502536932199</v>
+        <v>1.240079921784324</v>
       </c>
       <c r="C47">
-        <v>-0.6808541457117485</v>
+        <v>1.781645451402848</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.8239896367002556</v>
+        <v>0.1759349372651901</v>
       </c>
       <c r="C48">
-        <v>-2.061024720883433</v>
+        <v>0.4692017802050794</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.5008781656317108</v>
+        <v>-0.8083720384123868</v>
       </c>
       <c r="C49">
-        <v>0.193428352634616</v>
+        <v>0.9508406111622922</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.5854211991008988</v>
+        <v>-0.490701309401037</v>
       </c>
       <c r="C50">
-        <v>0.4059499545193073</v>
+        <v>-0.6218271727604321</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.4568826031075209</v>
+        <v>0.3292579351887873</v>
       </c>
       <c r="C51">
-        <v>0.5201747662219046</v>
+        <v>-0.1878928736425524</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.474590379609479</v>
+        <v>-0.4712690129621708</v>
       </c>
       <c r="C52">
-        <v>-0.3089446627721271</v>
+        <v>-0.6231315294083432</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.174158638839643</v>
+        <v>-1.368595797258142</v>
       </c>
       <c r="C53">
-        <v>0.5604415936931552</v>
+        <v>1.608822786115104</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.6604236558906786</v>
+        <v>0.6166403831945958</v>
       </c>
       <c r="C54">
-        <v>3.26987696019843</v>
+        <v>0.5808883618807861</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.4117298193868265</v>
+        <v>1.275427788057832</v>
       </c>
       <c r="C55">
-        <v>0.7836621301148879</v>
+        <v>0.07764122932110673</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.7087864231635297</v>
+        <v>-0.5217372692860898</v>
       </c>
       <c r="C56">
-        <v>-0.2977672303790513</v>
+        <v>-0.7338092783542924</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>-0.370409747410307</v>
+        <v>-0.4775610784459103</v>
       </c>
       <c r="C57">
-        <v>1.477576238789383</v>
+        <v>0.0266716849879523</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.1785412111751573</v>
+        <v>-0.3734191769215677</v>
       </c>
       <c r="C58">
-        <v>1.945369831815658</v>
+        <v>0.07816910417343771</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>-1.007762813260146</v>
+        <v>0.725099275593179</v>
       </c>
       <c r="C59">
-        <v>-0.6267940158261409</v>
+        <v>1.387085771646791</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.3674477536948111</v>
+        <v>1.325670948298006</v>
       </c>
       <c r="C60">
-        <v>1.889673929884091</v>
+        <v>0.09398810797976787</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>1.382979347703241</v>
+        <v>1.94537647857763</v>
       </c>
       <c r="C61">
-        <v>0.3743000048386333</v>
+        <v>1.297589211648136</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>-0.5701305516773395</v>
+        <v>1.148807238715142</v>
       </c>
       <c r="C62">
-        <v>2.078806302513254</v>
+        <v>0.8729542191722059</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.5247311110913984</v>
+        <v>0.4485236484510409</v>
       </c>
       <c r="C63">
-        <v>0.5489514528500848</v>
+        <v>-0.4202869496085729</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>-0.4152062420531847</v>
+        <v>-0.7600692238620635</v>
       </c>
       <c r="C64">
-        <v>-0.6543507177957146</v>
+        <v>0.328708684865035</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>-0.03774493961950554</v>
+        <v>0.343558667757233</v>
       </c>
       <c r="C65">
-        <v>-1.525358565779642</v>
+        <v>-0.3616052081822245</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.4767342228977521</v>
+        <v>0.9452763244836505</v>
       </c>
       <c r="C66">
-        <v>0.7552998487835932</v>
+        <v>-2.050921759139672</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>-1.99136892438547</v>
+        <v>-1.937924511615761</v>
       </c>
       <c r="C67">
-        <v>-2.046610478755063</v>
+        <v>1.031021986578535</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>0.5604524149839986</v>
+        <v>0.3450381625065054</v>
       </c>
       <c r="C68">
-        <v>0.07157918509545584</v>
+        <v>-0.4871087077640237</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>-0.7601808719782456</v>
+        <v>1.37111056837476</v>
       </c>
       <c r="C69">
-        <v>-0.4904215782916716</v>
+        <v>-1.455705852344985</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>-1.124537778716721</v>
+        <v>-0.6474550377087178</v>
       </c>
       <c r="C70">
-        <v>-2.111629215136835</v>
+        <v>0.7506291440935022</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.7081475015329528</v>
+        <v>-0.7663913629557406</v>
       </c>
       <c r="C71">
-        <v>-2.050231376505171</v>
+        <v>-0.08327361625535518</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-0.01275395268864413</v>
+        <v>1.384044324936698</v>
       </c>
       <c r="C72">
-        <v>-0.884928244153761</v>
+        <v>-2.076320199004982</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-2.455392846105619</v>
+        <v>-2.039810234866939</v>
       </c>
       <c r="C73">
-        <v>-0.05928611331334902</v>
+        <v>-0.155120581197058</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.1089652914471488</v>
+        <v>-0.587195225248915</v>
       </c>
       <c r="C74">
-        <v>-0.9840165474250118</v>
+        <v>0.3273257032620404</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-1.123235120715922</v>
+        <v>0.2852092365854073</v>
       </c>
       <c r="C75">
-        <v>-0.6430684169361185</v>
+        <v>0.5705124651276661</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>1.168025523683893</v>
+        <v>0.1162822110865301</v>
       </c>
       <c r="C76">
-        <v>0.6044102461908821</v>
+        <v>0.2391072092610493</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>0.5629947148787471</v>
+        <v>1.240762430324962</v>
       </c>
       <c r="C77">
-        <v>-1.068450950240435</v>
+        <v>-1.260773259051712</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>1.040234320112613</v>
+        <v>-2.705283419612534</v>
       </c>
       <c r="C78">
-        <v>1.804107975080672</v>
+        <v>0.8480013980010661</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.6588066387763895</v>
+        <v>0.5398589058301817</v>
       </c>
       <c r="C79">
-        <v>-0.1668584258335912</v>
+        <v>-0.01955813572203005</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.2842604649032366</v>
+        <v>0.2744369947139765</v>
       </c>
       <c r="C80">
-        <v>0.1863758240047461</v>
+        <v>0.05357843150087784</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-0.5976976836157961</v>
+        <v>1.2217667243071</v>
       </c>
       <c r="C81">
-        <v>-2.073495343435679</v>
+        <v>0.09554100288574163</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>-1.05586067818505</v>
+        <v>-1.455512465998787</v>
       </c>
       <c r="C82">
-        <v>-1.209310810130574</v>
+        <v>-0.3620682136900485</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>1.009831365698002</v>
+        <v>-0.5713108465977632</v>
       </c>
       <c r="C83">
-        <v>-0.2868557948651908</v>
+        <v>-1.073161154399764</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.8038094765547241</v>
+        <v>1.186718647307216</v>
       </c>
       <c r="C84">
-        <v>1.180027888195325</v>
+        <v>0.203824265750045</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>-1.831739328651949</v>
+        <v>0.309400891516817</v>
       </c>
       <c r="C85">
-        <v>-2.890509466146192</v>
+        <v>-1.189740349113588</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>-1.66558092443322</v>
+        <v>-1.482085248324898</v>
       </c>
       <c r="C86">
-        <v>0.4063797637508761</v>
+        <v>0.5425061284467407</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>-1.127071305388615</v>
+        <v>0.3744188484543467</v>
       </c>
       <c r="C87">
-        <v>0.1707211117468069</v>
+        <v>0.4746394373998643</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>-0.9763910404905596</v>
+        <v>-0.8741545269252223</v>
       </c>
       <c r="C88">
-        <v>-1.310547130532541</v>
+        <v>0.6795519283974187</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>-0.3128945098515208</v>
+        <v>-0.01257733539065831</v>
       </c>
       <c r="C89">
-        <v>-0.04627942226602016</v>
+        <v>1.033390679317371</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>1.031581061581422</v>
+        <v>-1.481041960978312</v>
       </c>
       <c r="C90">
-        <v>-0.05274564152644416</v>
+        <v>0.8037239205250906</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.6724542604550705</v>
+        <v>0.656265120692635</v>
       </c>
       <c r="C91">
-        <v>-0.3888509852978403</v>
+        <v>-0.9718881076553592</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>-0.002757517992286438</v>
+        <v>2.436922107218385</v>
       </c>
       <c r="C92">
-        <v>0.459563522685817</v>
+        <v>-1.174518244212014</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>-0.7910821985240998</v>
+        <v>0.1551662816165626</v>
       </c>
       <c r="C93">
-        <v>0.06051676027352736</v>
+        <v>-0.08592523943304786</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.6010347554157832</v>
+        <v>-0.2623221667149525</v>
       </c>
       <c r="C94">
-        <v>-1.059827518762992</v>
+        <v>1.348511998244406</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>1.841009355312953</v>
+        <v>-1.599489991540813</v>
       </c>
       <c r="C95">
-        <v>-0.6312347495526459</v>
+        <v>0.7506964439298451</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>-0.04071358833500866</v>
+        <v>1.00469320709723</v>
       </c>
       <c r="C96">
-        <v>-1.01276468158486</v>
+        <v>-0.5538678888364759</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-0.8301953361199391</v>
+        <v>0.3904426657003521</v>
       </c>
       <c r="C97">
-        <v>-0.3854719830079498</v>
+        <v>0.1909198267666651</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>1.021390748390768</v>
+        <v>0.879312707736025</v>
       </c>
       <c r="C98">
-        <v>0.4996499959840093</v>
+        <v>-1.097207237559122</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>-1.066552693708275</v>
+        <v>-0.008253151816631268</v>
       </c>
       <c r="C99">
-        <v>0.06388006140610485</v>
+        <v>0.3216402744856354</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>1.935664636563713</v>
+        <v>0.1729118593702662</v>
       </c>
       <c r="C100">
-        <v>0.4569272417234121</v>
+        <v>0.08709380029155496</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.3731686968286861</v>
+        <v>-1.05885381191166</v>
       </c>
       <c r="C101">
-        <v>0.3127873762049546</v>
+        <v>1.589396670432582</v>
       </c>
     </row>
     <row r="102">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B102">
-        <v>-1.105016593493775</v>
+        <v>0.01978016697725505</v>
       </c>
       <c r="C102">
-        <v>0.8909246252330072</v>
+        <v>-0.02385866492079178</v>
       </c>
     </row>
     <row r="103">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B103">
-        <v>0.2215311247278852</v>
+        <v>-0.4973913373981216</v>
       </c>
       <c r="C103">
-        <v>0.9520859564736359</v>
+        <v>-0.2126438944319845</v>
       </c>
     </row>
     <row r="104">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="B104">
-        <v>-0.6414168479245371</v>
+        <v>-0.3121979240156087</v>
       </c>
       <c r="C104">
-        <v>-1.38956802834648</v>
+        <v>0.04488311940960603</v>
       </c>
     </row>
     <row r="105">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="B105">
-        <v>0.1540820226284415</v>
+        <v>-0.9163993544783053</v>
       </c>
       <c r="C105">
-        <v>-0.63298901751034</v>
+        <v>1.636484476949659</v>
       </c>
     </row>
     <row r="106">
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="B106">
-        <v>-0.02679897190762978</v>
+        <v>0.5664832432726996</v>
       </c>
       <c r="C106">
-        <v>0.1881428011864887</v>
+        <v>-1.02763637584938</v>
       </c>
     </row>
     <row r="107">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B107">
-        <v>-0.7516837027968285</v>
+        <v>-1.509333137756128</v>
       </c>
       <c r="C107">
-        <v>1.038767506346236</v>
+        <v>1.755489818226623</v>
       </c>
     </row>
     <row r="108">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="B108">
-        <v>-2.114789625845052</v>
+        <v>-0.9912865940882315</v>
       </c>
       <c r="C108">
-        <v>0.5692743275941853</v>
+        <v>1.4364576930924</v>
       </c>
     </row>
     <row r="109">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="B109">
-        <v>-0.2222531004657758</v>
+        <v>-1.961925511872947</v>
       </c>
       <c r="C109">
-        <v>-0.3654079678492151</v>
+        <v>0.4752753248133996</v>
       </c>
     </row>
     <row r="110">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.5129764119917062</v>
+        <v>-1.084563961801973</v>
       </c>
       <c r="C110">
-        <v>1.157928790086255</v>
+        <v>-0.04657306311828779</v>
       </c>
     </row>
     <row r="111">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>1.270945625199674</v>
+        <v>-0.3552214793876869</v>
       </c>
       <c r="C111">
-        <v>1.329253102105569</v>
+        <v>0.4011950955508801</v>
       </c>
     </row>
     <row r="112">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>-0.2859354290703799</v>
+        <v>0.1352177564188721</v>
       </c>
       <c r="C112">
-        <v>-1.191527106737178</v>
+        <v>1.178896215216132</v>
       </c>
     </row>
     <row r="113">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>-1.061134244244502</v>
+        <v>1.29911273544822</v>
       </c>
       <c r="C113">
-        <v>1.405220949010403</v>
+        <v>0.862606741213937</v>
       </c>
     </row>
     <row r="114">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.07668839461156431</v>
+        <v>0.7764808060721478</v>
       </c>
       <c r="C114">
-        <v>-0.4398265885203037</v>
+        <v>2.265247889022498</v>
       </c>
     </row>
     <row r="115">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>-2.137612652300951</v>
+        <v>1.007652670393957</v>
       </c>
       <c r="C115">
-        <v>0.1566415856841995</v>
+        <v>-0.4585701033169177</v>
       </c>
     </row>
     <row r="116">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>-0.8821758398379947</v>
+        <v>0.1882894054602586</v>
       </c>
       <c r="C116">
-        <v>-0.876273826133961</v>
+        <v>0.01242795318259655</v>
       </c>
     </row>
     <row r="117">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>-1.065904133179413</v>
+        <v>0.6855298460619127</v>
       </c>
       <c r="C117">
-        <v>-0.1552633425220867</v>
+        <v>-0.1449192416708502</v>
       </c>
     </row>
     <row r="118">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>-0.6356302585520226</v>
+        <v>0.8431888342279401</v>
       </c>
       <c r="C118">
-        <v>0.7983061552974273</v>
+        <v>-1.923180457864329</v>
       </c>
     </row>
     <row r="119">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.7035163813180223</v>
+        <v>-2.137081310581755</v>
       </c>
       <c r="C119">
-        <v>-0.745241603187514</v>
+        <v>1.237686825087859</v>
       </c>
     </row>
     <row r="120">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.1432725713421034</v>
+        <v>-0.2917946122894358</v>
       </c>
       <c r="C120">
-        <v>0.1026019163047793</v>
+        <v>0.1709810987670453</v>
       </c>
     </row>
     <row r="121">
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>-0.8984664324809838</v>
+        <v>-0.7560497467716842</v>
       </c>
       <c r="C121">
-        <v>0.1808841166553474</v>
+        <v>1.068515036733532</v>
       </c>
     </row>
     <row r="122">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>-0.1995447479391059</v>
+        <v>-0.7880026657241347</v>
       </c>
       <c r="C122">
-        <v>-0.769572204985686</v>
+        <v>-0.8915287890092336</v>
       </c>
     </row>
     <row r="123">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>2.691260904522959</v>
+        <v>1.109074666868558</v>
       </c>
       <c r="C123">
-        <v>-1.555635775779331</v>
+        <v>-0.6718894515405298</v>
       </c>
     </row>
     <row r="124">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>-1.118371002671096</v>
+        <v>-0.7067851193712539</v>
       </c>
       <c r="C124">
-        <v>-0.9279528012432927</v>
+        <v>0.5281598471150605</v>
       </c>
     </row>
     <row r="125">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>0.3436325526589042</v>
+        <v>0.4334219622308559</v>
       </c>
       <c r="C125">
-        <v>-0.5674317352070168</v>
+        <v>-0.9746147856745525</v>
       </c>
     </row>
     <row r="126">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>-0.2039910015021174</v>
+        <v>-0.5770746860826241</v>
       </c>
       <c r="C126">
-        <v>-0.3562404123179008</v>
+        <v>-1.042906699101129</v>
       </c>
     </row>
     <row r="127">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>1.26582542909252</v>
+        <v>0.198191497228372</v>
       </c>
       <c r="C127">
-        <v>-0.5843130290659131</v>
+        <v>-0.02387424174537436</v>
       </c>
     </row>
     <row r="128">
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>1.715875021960297</v>
+        <v>0.9722392334137483</v>
       </c>
       <c r="C128">
-        <v>-0.272974420534593</v>
+        <v>-0.4976980264423229</v>
       </c>
     </row>
     <row r="129">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>-0.07822599547638606</v>
+        <v>-1.181581432279925</v>
       </c>
       <c r="C129">
-        <v>-0.6456012476085162</v>
+        <v>0.5491279239056677</v>
       </c>
     </row>
     <row r="130">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>-0.2604070316785211</v>
+        <v>-1.573573430690544</v>
       </c>
       <c r="C130">
-        <v>-1.642389961913561</v>
+        <v>1.169686038083428</v>
       </c>
     </row>
     <row r="131">
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.2582820152012038</v>
+        <v>0.8018844932347774</v>
       </c>
       <c r="C131">
-        <v>0.7353590856913987</v>
+        <v>1.248442305685822</v>
       </c>
     </row>
     <row r="132">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.5421624710382719</v>
+        <v>0.1383565953433656</v>
       </c>
       <c r="C132">
-        <v>0.1220247652615764</v>
+        <v>-1.001132136373356</v>
       </c>
     </row>
     <row r="133">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>0.3124064453890569</v>
+        <v>0.114624756971684</v>
       </c>
       <c r="C133">
-        <v>0.1970782329076544</v>
+        <v>-0.9284207447202766</v>
       </c>
     </row>
     <row r="134">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>-0.07597386848244331</v>
+        <v>-0.5382713310460384</v>
       </c>
       <c r="C134">
-        <v>1.112960670045797</v>
+        <v>-0.8928413498202317</v>
       </c>
     </row>
     <row r="135">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>-1.730030600478279</v>
+        <v>-0.8234910524533833</v>
       </c>
       <c r="C135">
-        <v>0.9348156351597809</v>
+        <v>2.10522559590513</v>
       </c>
     </row>
     <row r="136">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>-1.813179264336012</v>
+        <v>1.860610335533754</v>
       </c>
       <c r="C136">
-        <v>-2.052281946004182</v>
+        <v>-1.404491542417996</v>
       </c>
     </row>
     <row r="137">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B137">
-        <v>0.1168062600003075</v>
+        <v>-0.7889153609455346</v>
       </c>
       <c r="C137">
-        <v>1.365216506810345</v>
+        <v>0.9756749545098156</v>
       </c>
     </row>
     <row r="138">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>1.270404371310346</v>
+        <v>-0.5835418895621706</v>
       </c>
       <c r="C138">
-        <v>1.947867353993979</v>
+        <v>0.2775932451907109</v>
       </c>
     </row>
     <row r="139">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>0.8874280258758754</v>
+        <v>1.151099841744042</v>
       </c>
       <c r="C139">
-        <v>-0.7352547961113736</v>
+        <v>0.2354917337604051</v>
       </c>
     </row>
     <row r="140">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>0.9318003181199318</v>
+        <v>0.263307540813236</v>
       </c>
       <c r="C140">
-        <v>-1.494728018991519</v>
+        <v>0.5047387731703969</v>
       </c>
     </row>
     <row r="141">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>1.607220865461197</v>
+        <v>1.455853685627736</v>
       </c>
       <c r="C141">
-        <v>-0.1845185794171396</v>
+        <v>0.202856726906569</v>
       </c>
     </row>
     <row r="142">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>-1.105120300983977</v>
+        <v>0.3590977687221423</v>
       </c>
       <c r="C142">
-        <v>-0.005274546599270063</v>
+        <v>0.01239040427379001</v>
       </c>
     </row>
     <row r="143">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>0.02640020804624723</v>
+        <v>2.075434360619006</v>
       </c>
       <c r="C143">
-        <v>-0.6334618485396747</v>
+        <v>-1.46119372441076</v>
       </c>
     </row>
     <row r="144">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>-0.2229028120720042</v>
+        <v>1.830035442894112</v>
       </c>
       <c r="C144">
-        <v>-1.086853524444974</v>
+        <v>0.412583456499397</v>
       </c>
     </row>
     <row r="145">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>-0.1469915569618835</v>
+        <v>-0.8342727572905798</v>
       </c>
       <c r="C145">
-        <v>-0.5817300300319661</v>
+        <v>1.67360230805549</v>
       </c>
     </row>
     <row r="146">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>-0.2930509939842763</v>
+        <v>-0.04482447583950229</v>
       </c>
       <c r="C146">
-        <v>0.1090868285187743</v>
+        <v>0.4384151947224302</v>
       </c>
     </row>
     <row r="147">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>0.2193662629107341</v>
+        <v>-1.567056509527353</v>
       </c>
       <c r="C147">
-        <v>1.333393065651541</v>
+        <v>0.9972085182198234</v>
       </c>
     </row>
     <row r="148">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>1.47178478471121</v>
+        <v>1.718739582152584</v>
       </c>
       <c r="C148">
-        <v>-0.05922396562536113</v>
+        <v>-1.964134255052826</v>
       </c>
     </row>
     <row r="149">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>-0.469164914636018</v>
+        <v>0.09790058972667713</v>
       </c>
       <c r="C149">
-        <v>-0.6171331491916795</v>
+        <v>0.8247177590785411</v>
       </c>
     </row>
     <row r="150">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="B150">
-        <v>-0.8835922904942324</v>
+        <v>0.2250664063308178</v>
       </c>
       <c r="C150">
-        <v>-1.635903739437848</v>
+        <v>0.1964716523768995</v>
       </c>
     </row>
     <row r="151">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="B151">
-        <v>1.051086414667062</v>
+        <v>-0.7364888410933195</v>
       </c>
       <c r="C151">
-        <v>0.1082304934705337</v>
+        <v>-0.6798057644503945</v>
       </c>
     </row>
     <row r="152">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="B152">
-        <v>-0.3774074232346831</v>
+        <v>0.1123226816782437</v>
       </c>
       <c r="C152">
-        <v>0.7382194196216564</v>
+        <v>-1.070322510476331</v>
       </c>
     </row>
     <row r="153">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B153">
-        <v>0.8577682296183257</v>
+        <v>0.1218515366208325</v>
       </c>
       <c r="C153">
-        <v>0.8997288357783124</v>
+        <v>0.2440734484074056</v>
       </c>
     </row>
     <row r="154">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="B154">
-        <v>-1.151700452212781</v>
+        <v>-0.6016219823584222</v>
       </c>
       <c r="C154">
-        <v>-0.7883765602610973</v>
+        <v>-0.1620529833732916</v>
       </c>
     </row>
     <row r="155">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="B155">
-        <v>-0.2808091550421487</v>
+        <v>-0.6250287773992711</v>
       </c>
       <c r="C155">
-        <v>0.894724259925863</v>
+        <v>0.1931674647809438</v>
       </c>
     </row>
     <row r="156">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="B156">
-        <v>2.209820929025422</v>
+        <v>-0.1140792471024163</v>
       </c>
       <c r="C156">
-        <v>-0.8586691951079027</v>
+        <v>0.4311467261040139</v>
       </c>
     </row>
     <row r="157">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="B157">
-        <v>-1.032720462906023</v>
+        <v>0.4037638108799395</v>
       </c>
       <c r="C157">
-        <v>-0.2177796487134279</v>
+        <v>1.939369871906772</v>
       </c>
     </row>
     <row r="158">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>-0.7217609097528036</v>
+        <v>-1.968532959897739</v>
       </c>
       <c r="C158">
-        <v>-0.7612186559212354</v>
+        <v>0.2554628958726504</v>
       </c>
     </row>
     <row r="159">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>-0.6897125351950278</v>
+        <v>-0.1000264405337535</v>
       </c>
       <c r="C159">
-        <v>-1.535085091563893</v>
+        <v>-1.902631099655719</v>
       </c>
     </row>
     <row r="160">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>-0.07363150315171754</v>
+        <v>0.7931969757706618</v>
       </c>
       <c r="C160">
-        <v>-1.798807012586422</v>
+        <v>1.200206001951456</v>
       </c>
     </row>
     <row r="161">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>1.181485424616421</v>
+        <v>0.04966817313917395</v>
       </c>
       <c r="C161">
-        <v>1.124875191658637</v>
+        <v>0.05299865201062597</v>
       </c>
     </row>
     <row r="162">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>-0.3120379705942026</v>
+        <v>-0.8796725024280555</v>
       </c>
       <c r="C162">
-        <v>-1.838752152791266</v>
+        <v>-1.90497805800719</v>
       </c>
     </row>
     <row r="163">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>-0.3294284080918572</v>
+        <v>0.4397201068224347</v>
       </c>
       <c r="C163">
-        <v>-0.6265273752247855</v>
+        <v>-0.8856313998521561</v>
       </c>
     </row>
     <row r="164">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>0.9252428304645567</v>
+        <v>-0.566680603587551</v>
       </c>
       <c r="C164">
-        <v>0.8404183946781831</v>
+        <v>-0.3654435433425459</v>
       </c>
     </row>
     <row r="165">
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B165">
-        <v>0.09246955764406198</v>
+        <v>1.488313764546807</v>
       </c>
       <c r="C165">
-        <v>-1.00227824205847</v>
+        <v>0.4319227551898958</v>
       </c>
     </row>
     <row r="166">
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="B166">
-        <v>1.770610326541739</v>
+        <v>-0.2795682699276875</v>
       </c>
       <c r="C166">
-        <v>-0.4156726808230642</v>
+        <v>-0.381021617833157</v>
       </c>
     </row>
     <row r="167">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="B167">
-        <v>-0.3579232707158678</v>
+        <v>-0.6961933288931503</v>
       </c>
       <c r="C167">
-        <v>-0.9241089864506752</v>
+        <v>-1.135120736809299</v>
       </c>
     </row>
     <row r="168">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="B168">
-        <v>-0.2402519382525888</v>
+        <v>-0.7158659308541404</v>
       </c>
       <c r="C168">
-        <v>-0.5373531825881895</v>
+        <v>0.1136963539186803</v>
       </c>
     </row>
     <row r="169">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="B169">
-        <v>0.1208238808273399</v>
+        <v>-0.3996204935811079</v>
       </c>
       <c r="C169">
-        <v>-1.132220077161862</v>
+        <v>0.4740168518360559</v>
       </c>
     </row>
     <row r="170">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="B170">
-        <v>1.740398692153287</v>
+        <v>-0.4533557302693831</v>
       </c>
       <c r="C170">
-        <v>-0.2985941161370571</v>
+        <v>-0.0400668766237646</v>
       </c>
     </row>
     <row r="171">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="B171">
-        <v>0.2149746743521197</v>
+        <v>0.2459735886319258</v>
       </c>
       <c r="C171">
-        <v>1.897896915908581</v>
+        <v>-0.8455295574440015</v>
       </c>
     </row>
     <row r="172">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B172">
-        <v>0.05145489404961763</v>
+        <v>-0.7055604376067198</v>
       </c>
       <c r="C172">
-        <v>0.4225396744107132</v>
+        <v>1.272324196340541</v>
       </c>
     </row>
     <row r="173">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B173">
-        <v>1.053953669912777</v>
+        <v>0.6734476033210546</v>
       </c>
       <c r="C173">
-        <v>-1.280834978506882</v>
+        <v>-0.6627729066793087</v>
       </c>
     </row>
     <row r="174">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>0.06933094523736086</v>
+        <v>2.654655175954312</v>
       </c>
       <c r="C174">
-        <v>0.953025717062882</v>
+        <v>-0.182245121367648</v>
       </c>
     </row>
     <row r="175">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>-1.048731785884386</v>
+        <v>-0.9087330202218142</v>
       </c>
       <c r="C175">
-        <v>0.1782090136969484</v>
+        <v>-1.837338849857108</v>
       </c>
     </row>
     <row r="176">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="B176">
-        <v>0.07467714754041123</v>
+        <v>-1.393172294870546</v>
       </c>
       <c r="C176">
-        <v>-0.345891352255792</v>
+        <v>0.8457788136404901</v>
       </c>
     </row>
     <row r="177">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B177">
-        <v>2.334940959966874</v>
+        <v>-1.372159866284387</v>
       </c>
       <c r="C177">
-        <v>2.072569830721781</v>
+        <v>0.6110303204934115</v>
       </c>
     </row>
     <row r="178">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="B178">
-        <v>-0.1973068310533179</v>
+        <v>-0.2043910167534894</v>
       </c>
       <c r="C178">
-        <v>-0.2561294378108974</v>
+        <v>-2.190008453955394</v>
       </c>
     </row>
     <row r="179">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="B179">
-        <v>-0.8015153972477769</v>
+        <v>-0.3929533706631083</v>
       </c>
       <c r="C179">
-        <v>1.462683611616531</v>
+        <v>-0.5089561369959221</v>
       </c>
     </row>
     <row r="180">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="B180">
-        <v>-0.5426443409058009</v>
+        <v>-0.8380553946757276</v>
       </c>
       <c r="C180">
-        <v>0.609397327270279</v>
+        <v>-0.2610150897918825</v>
       </c>
     </row>
     <row r="181">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>-0.5347234483728426</v>
+        <v>0.5992104561897231</v>
       </c>
       <c r="C181">
-        <v>1.754776861294328</v>
+        <v>-0.805814480634692</v>
       </c>
     </row>
     <row r="182">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>0.3893989750434422</v>
+        <v>-1.682061717391716</v>
       </c>
       <c r="C182">
-        <v>0.09144111628835187</v>
+        <v>1.39511395303842</v>
       </c>
     </row>
     <row r="183">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="B183">
-        <v>0.3367854331944231</v>
+        <v>-0.7350241319670753</v>
       </c>
       <c r="C183">
-        <v>0.0671833751376115</v>
+        <v>0.5485959743084123</v>
       </c>
     </row>
     <row r="184">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B184">
-        <v>-0.6400382549645643</v>
+        <v>-0.1779413467531618</v>
       </c>
       <c r="C184">
-        <v>0.1360506307511878</v>
+        <v>-0.07885705921482798</v>
       </c>
     </row>
     <row r="185">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="B185">
-        <v>0.1053136855797666</v>
+        <v>0.5036837168161586</v>
       </c>
       <c r="C185">
-        <v>-1.042489158534391</v>
+        <v>-0.4955180323114486</v>
       </c>
     </row>
     <row r="186">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="B186">
-        <v>-0.8513719455378754</v>
+        <v>0.1864741395248317</v>
       </c>
       <c r="C186">
-        <v>0.2064632821845928</v>
+        <v>-0.9473844694528618</v>
       </c>
     </row>
     <row r="187">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="B187">
-        <v>-0.7454152572589027</v>
+        <v>-0.3106710919148998</v>
       </c>
       <c r="C187">
-        <v>-0.1490459751450067</v>
+        <v>-0.5791029074980314</v>
       </c>
     </row>
     <row r="188">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="B188">
-        <v>-2.096811905715902</v>
+        <v>2.033054424268706</v>
       </c>
       <c r="C188">
-        <v>0.2446496101571749</v>
+        <v>-1.144230113613066</v>
       </c>
     </row>
     <row r="189">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="B189">
-        <v>-1.453790068439106</v>
+        <v>-0.7910659433763678</v>
       </c>
       <c r="C189">
-        <v>0.7110130157835099</v>
+        <v>1.165911994578521</v>
       </c>
     </row>
     <row r="190">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="B190">
-        <v>-0.4226490891200246</v>
+        <v>0.9782515062114238</v>
       </c>
       <c r="C190">
-        <v>1.979241961655672</v>
+        <v>-0.7597873053217692</v>
       </c>
     </row>
     <row r="191">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="B191">
-        <v>-0.2330460514667152</v>
+        <v>0.1912137146912099</v>
       </c>
       <c r="C191">
-        <v>-1.184630328038407</v>
+        <v>0.1612004545847203</v>
       </c>
     </row>
     <row r="192">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="B192">
-        <v>-0.2133950212940574</v>
+        <v>0.209892034531174</v>
       </c>
       <c r="C192">
-        <v>1.128283090260233</v>
+        <v>0.5708557720110186</v>
       </c>
     </row>
     <row r="193">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="B193">
-        <v>2.435780959767054</v>
+        <v>0.2311281412798253</v>
       </c>
       <c r="C193">
-        <v>-0.008253861668969005</v>
+        <v>-1.093336603430121</v>
       </c>
     </row>
     <row r="194">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="B194">
-        <v>0.5653846086647915</v>
+        <v>-0.3083899081346134</v>
       </c>
       <c r="C194">
-        <v>-0.1344895258674536</v>
+        <v>-0.2284925478470908</v>
       </c>
     </row>
     <row r="195">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="B195">
-        <v>1.252135512901533</v>
+        <v>0.6153922448088688</v>
       </c>
       <c r="C195">
-        <v>-1.297298474037377</v>
+        <v>0.5494913362700653</v>
       </c>
     </row>
     <row r="196">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="B196">
-        <v>0.9041056252530942</v>
+        <v>-0.2247140508682942</v>
       </c>
       <c r="C196">
-        <v>-0.1860347801194809</v>
+        <v>1.498954958931953</v>
       </c>
     </row>
     <row r="197">
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="B197">
-        <v>-0.6284320257766385</v>
+        <v>-0.3790027251162115</v>
       </c>
       <c r="C197">
-        <v>1.32800221002664</v>
+        <v>0.2716165901851069</v>
       </c>
     </row>
     <row r="198">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>-0.4016449938039523</v>
+        <v>-0.4518763777172361</v>
       </c>
       <c r="C198">
-        <v>1.875510003614234</v>
+        <v>0.1338919927080878</v>
       </c>
     </row>
     <row r="199">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>-0.7487551031016628</v>
+        <v>0.065191089799381</v>
       </c>
       <c r="C199">
-        <v>0.6191699274225519</v>
+        <v>0.7165093505708288</v>
       </c>
     </row>
     <row r="200">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>-0.4305148019270794</v>
+        <v>1.076443917055852</v>
       </c>
       <c r="C200">
-        <v>0.8155778825747575</v>
+        <v>0.0307773318932606</v>
       </c>
     </row>
     <row r="201">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>-0.1436584435954631</v>
+        <v>-0.3155478101045224</v>
       </c>
       <c r="C201">
-        <v>0.226551856011212</v>
+        <v>-0.3860611599572588</v>
       </c>
     </row>
   </sheetData>
